--- a/data/trans_orig/P1430-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P1430-Clase-trans_orig.xlsx
@@ -536,7 +536,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de cirrosis en 2012</t>
+          <t>Población con diagnóstico de cirrosis en 2012 (tasa de respuesta: 99,97%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -731,97 +731,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2072</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0,47%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>2125</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>0,68%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>2098</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>435139</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>437211</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>312329</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>314454</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>749567</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>751665</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>5070</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1114,7 +1114,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7641</t>
+          <t>7142</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1129,7 +1129,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1009</t>
+          <t>1003</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8628</t>
+          <t>8577</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1164,7 +1164,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,13%</t>
         </is>
       </c>
     </row>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>413717</t>
+          <t>413727</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>330370</t>
+          <t>330869</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>748180</t>
+          <t>748231</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>755799</t>
+          <t>755805</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,87%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>938</t>
+          <t>926</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8675</t>
+          <t>8668</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1457,7 +1457,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5258</t>
+          <t>5323</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1037</t>
+          <t>1044</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10267</t>
+          <t>10340</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1507,7 +1507,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,16%</t>
         </is>
       </c>
     </row>
@@ -1530,12 +1530,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>620740</t>
+          <t>620747</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>628477</t>
+          <t>628489</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1565,7 +1565,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>254871</t>
+          <t>254806</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>879277</t>
+          <t>879204</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>888507</t>
+          <t>888500</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,84%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1760,12 +1760,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10438</t>
+          <t>10341</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>29278</t>
+          <t>30687</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1775,12 +1775,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3029</t>
+          <t>3054</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>14462</t>
+          <t>14336</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1815,7 +1815,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>16469</t>
+          <t>15627</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>37450</t>
+          <t>37696</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,96%</t>
         </is>
       </c>
     </row>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1129731</t>
+          <t>1128322</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1148571</t>
+          <t>1148668</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,12 +1888,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,35%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,11%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>750260</t>
+          <t>750386</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>761693</t>
+          <t>761668</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,13%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1886281</t>
+          <t>1886035</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1907262</t>
+          <t>1908104</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,19%</t>
         </is>
       </c>
     </row>
@@ -2108,7 +2108,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8324</t>
+          <t>8084</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2123,7 +2123,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2138,12 +2138,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>943</t>
+          <t>949</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9221</t>
+          <t>9635</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2158,7 +2158,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2270</t>
+          <t>2124</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>13030</t>
+          <t>12774</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2188,12 +2188,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,01%</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>502272</t>
+          <t>502512</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2231,7 +2231,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2251,12 +2251,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>751025</t>
+          <t>750611</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>759303</t>
+          <t>759297</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1257813</t>
+          <t>1258069</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1268573</t>
+          <t>1268719</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2301,12 +2301,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,82%</t>
+          <t>99,83%</t>
         </is>
       </c>
     </row>
@@ -2446,12 +2446,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1926</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2461,12 +2461,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2481,12 +2481,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4135</t>
+          <t>4260</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>16552</t>
+          <t>17940</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2516,12 +2516,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4129</t>
+          <t>3251</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>16375</t>
+          <t>15822</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,15%</t>
         </is>
       </c>
     </row>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>264956</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>266882</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2574,12 +2574,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2594,12 +2594,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1092799</t>
+          <t>1091411</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1105216</t>
+          <t>1105091</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2609,12 +2609,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,62%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2629,12 +2629,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1359858</t>
+          <t>1360411</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1372104</t>
+          <t>1372982</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2644,12 +2644,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,76%</t>
         </is>
       </c>
     </row>
@@ -2789,12 +2789,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>16503</t>
+          <t>14878</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>37260</t>
+          <t>37718</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2804,12 +2804,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>13822</t>
+          <t>13791</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>33959</t>
+          <t>32430</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2844,7 +2844,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2859,12 +2859,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>35182</t>
+          <t>34634</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>63470</t>
+          <t>63120</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2902,12 +2902,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3384650</t>
+          <t>3384192</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3405407</t>
+          <t>3407032</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2917,12 +2917,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,57%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2937,12 +2937,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3512956</t>
+          <t>3514485</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3533093</t>
+          <t>3533124</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2952,7 +2952,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -2972,12 +2972,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6905355</t>
+          <t>6905705</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6933643</t>
+          <t>6934191</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3171,7 +3171,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de cirrosis en 2016</t>
+          <t>Población con diagnóstico de cirrosis en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>923</t>
+          <t>917</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10167</t>
+          <t>11020</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3406,7 +3406,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5433</t>
+          <t>6441</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3421,7 +3421,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1835</t>
+          <t>1829</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12536</t>
+          <t>13406</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3456,7 +3456,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,73%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>418925</t>
+          <t>418072</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>428169</t>
+          <t>428175</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,78%</t>
+          <t>99,79%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>341622</t>
+          <t>340614</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -3529,7 +3529,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>763611</t>
+          <t>762741</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>774312</t>
+          <t>774318</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>972</t>
+          <t>958</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11760</t>
+          <t>10451</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>951</t>
+          <t>955</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>10568</t>
+          <t>11038</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3799,7 +3799,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,47%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>365467</t>
+          <t>366776</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>376255</t>
+          <t>376269</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>97,23%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>99,75%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>370249</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>372273</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>738932</t>
+          <t>738462</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>748549</t>
+          <t>748545</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3907,7 +3907,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1012</t>
+          <t>1137</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9693</t>
+          <t>10018</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4092,7 +4092,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10324</t>
+          <t>11392</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4107,7 +4107,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3068</t>
+          <t>2761</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>15941</t>
+          <t>15448</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,25%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>512221</t>
+          <t>511896</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>520902</t>
+          <t>520777</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,81%</t>
+          <t>99,78%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4200,7 +4200,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>155799</t>
+          <t>154731</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -4215,7 +4215,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,79%</t>
+          <t>93,14%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>672095</t>
+          <t>672588</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>684968</t>
+          <t>685275</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,6%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4315</t>
+          <t>4321</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18976</t>
+          <t>18670</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4415,7 +4415,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4435,7 +4435,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5006</t>
+          <t>4263</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4450,7 +4450,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5127</t>
+          <t>5136</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>19383</t>
+          <t>20129</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4485,7 +4485,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,02%</t>
         </is>
       </c>
     </row>
@@ -4508,12 +4508,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1130662</t>
+          <t>1130968</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1145323</t>
+          <t>1145317</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4523,7 +4523,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -4543,7 +4543,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>820870</t>
+          <t>821613</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -4558,7 +4558,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,48%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -4578,12 +4578,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1956131</t>
+          <t>1955385</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1970387</t>
+          <t>1970378</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4593,7 +4593,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>98,98%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>967</t>
+          <t>1235</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10076</t>
+          <t>10464</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2033</t>
+          <t>2004</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>12308</t>
+          <t>12608</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4857</t>
+          <t>4921</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>17869</t>
+          <t>17611</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4828,7 +4828,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,3%</t>
         </is>
       </c>
     </row>
@@ -4851,12 +4851,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>610630</t>
+          <t>610242</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>619739</t>
+          <t>619471</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4866,12 +4866,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,84%</t>
+          <t>99,8%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4886,12 +4886,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>725936</t>
+          <t>725636</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>736211</t>
+          <t>736240</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4901,12 +4901,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>99,73%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4921,12 +4921,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1341081</t>
+          <t>1341339</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1354093</t>
+          <t>1354029</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4936,7 +4936,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -5081,97 +5081,97 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>2322</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>8441</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>0,21%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>0,7%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>0,78%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="R19" s="2" t="inlineStr">
         <is>
           <t>2322</t>
         </is>
       </c>
-      <c r="L19" s="2" t="inlineStr">
+      <c r="S19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>8385</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>0,21%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>8319</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>0,17%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>0,77%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>2322</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>8223</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>0,17%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,61%</t>
         </is>
       </c>
     </row>
@@ -5194,12 +5194,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>285126</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>287145</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5209,12 +5209,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5229,7 +5229,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1073640</t>
+          <t>1073584</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -5244,7 +5244,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1360947</t>
+          <t>1360851</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -5279,7 +5279,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,39%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -5424,12 +5424,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>16649</t>
+          <t>15617</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>39252</t>
+          <t>36370</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5439,12 +5439,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5459,12 +5459,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>7571</t>
+          <t>7438</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>24233</t>
+          <t>23484</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5479,7 +5479,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5494,12 +5494,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>26104</t>
+          <t>27216</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>54067</t>
+          <t>54848</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5509,12 +5509,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,79%</t>
         </is>
       </c>
     </row>
@@ -5537,12 +5537,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3346470</t>
+          <t>3349352</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3369073</t>
+          <t>3370105</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5552,12 +5552,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,54%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5572,12 +5572,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3507363</t>
+          <t>3508112</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3524025</t>
+          <t>3524158</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5587,7 +5587,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6863251</t>
+          <t>6862470</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6891214</t>
+          <t>6890102</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,21%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,61%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1430-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P1430-Clase-trans_orig.xlsx
@@ -1079,7 +1079,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5070</t>
+          <t>5335</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1114,7 +1114,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7142</t>
+          <t>6927</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1129,7 +1129,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1003</t>
+          <t>1011</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8577</t>
+          <t>8478</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1164,7 +1164,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,12%</t>
         </is>
       </c>
     </row>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>413727</t>
+          <t>413462</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>330869</t>
+          <t>331084</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>748231</t>
+          <t>748330</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>755805</t>
+          <t>755797</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>926</t>
+          <t>945</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8668</t>
+          <t>8498</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1457,7 +1457,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5323</t>
+          <t>4724</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1044</t>
+          <t>1045</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10340</t>
+          <t>9353</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1507,7 +1507,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,05%</t>
         </is>
       </c>
     </row>
@@ -1530,12 +1530,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>620747</t>
+          <t>620917</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>628489</t>
+          <t>628470</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1565,7 +1565,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>254806</t>
+          <t>255405</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>98,18%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>879204</t>
+          <t>880191</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>888500</t>
+          <t>888499</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1760,12 +1760,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10341</t>
+          <t>9519</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>30687</t>
+          <t>29568</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1775,12 +1775,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3054</t>
+          <t>3073</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>14336</t>
+          <t>13463</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1815,7 +1815,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>15627</t>
+          <t>15678</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>37696</t>
+          <t>40126</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,09%</t>
         </is>
       </c>
     </row>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1128322</t>
+          <t>1129441</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1148668</t>
+          <t>1149490</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,12 +1888,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>750386</t>
+          <t>751259</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>761668</t>
+          <t>761649</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1886035</t>
+          <t>1883605</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1908104</t>
+          <t>1908053</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1958,7 +1958,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>97,91%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2103,12 +2103,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>982</t>
+          <t>981</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8084</t>
+          <t>9221</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2123,7 +2123,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2138,12 +2138,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>949</t>
+          <t>939</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9635</t>
+          <t>8733</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2158,7 +2158,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2124</t>
+          <t>2245</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>12774</t>
+          <t>12754</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2188,12 +2188,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,0%</t>
         </is>
       </c>
     </row>
@@ -2216,12 +2216,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>502512</t>
+          <t>501375</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>509614</t>
+          <t>509615</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2231,7 +2231,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2251,12 +2251,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>750611</t>
+          <t>751513</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>759297</t>
+          <t>759307</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1258069</t>
+          <t>1258089</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1268719</t>
+          <t>1268598</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2301,12 +2301,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,83%</t>
+          <t>99,82%</t>
         </is>
       </c>
     </row>
@@ -2426,7 +2426,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2481,12 +2481,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4260</t>
+          <t>4196</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>17940</t>
+          <t>16079</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2516,12 +2516,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3251</t>
+          <t>4171</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>15822</t>
+          <t>16155</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,17%</t>
         </is>
       </c>
     </row>
@@ -2594,12 +2594,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1091411</t>
+          <t>1093272</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1105091</t>
+          <t>1105155</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2609,7 +2609,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2629,12 +2629,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1360411</t>
+          <t>1360078</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1372982</t>
+          <t>1372062</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2644,12 +2644,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,76%</t>
+          <t>99,7%</t>
         </is>
       </c>
     </row>
@@ -2789,12 +2789,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>14878</t>
+          <t>15952</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>37718</t>
+          <t>38245</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2804,12 +2804,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>13791</t>
+          <t>13971</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>32430</t>
+          <t>33788</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2844,7 +2844,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2859,12 +2859,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>34634</t>
+          <t>33732</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>63120</t>
+          <t>62450</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2874,12 +2874,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,9%</t>
         </is>
       </c>
     </row>
@@ -2902,12 +2902,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3384192</t>
+          <t>3383665</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3407032</t>
+          <t>3405958</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2917,12 +2917,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,53%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2937,12 +2937,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3514485</t>
+          <t>3513127</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3533124</t>
+          <t>3532944</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2952,7 +2952,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -2972,12 +2972,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6905705</t>
+          <t>6906375</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6934191</t>
+          <t>6935093</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2987,12 +2987,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,52%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>917</t>
+          <t>933</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11020</t>
+          <t>11280</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3406,7 +3406,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6441</t>
+          <t>6252</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3421,7 +3421,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1829</t>
+          <t>1859</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13406</t>
+          <t>12661</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3456,7 +3456,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,63%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>418072</t>
+          <t>417812</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>428175</t>
+          <t>428159</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,79%</t>
+          <t>99,78%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>340614</t>
+          <t>340803</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -3529,7 +3529,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>762741</t>
+          <t>763486</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>774318</t>
+          <t>774288</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>958</t>
+          <t>947</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10451</t>
+          <t>10718</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>955</t>
+          <t>947</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>11038</t>
+          <t>10842</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3799,7 +3799,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,45%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>366776</t>
+          <t>366509</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>376269</t>
+          <t>376280</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3837,7 +3837,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>738462</t>
+          <t>738658</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>748545</t>
+          <t>748553</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3907,7 +3907,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1137</t>
+          <t>1030</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10018</t>
+          <t>9963</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4092,7 +4092,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11392</t>
+          <t>14954</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4107,7 +4107,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2761</t>
+          <t>2862</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>15448</t>
+          <t>16013</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,33%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>511896</t>
+          <t>511951</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>520777</t>
+          <t>520884</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,78%</t>
+          <t>99,8%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4200,7 +4200,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>154731</t>
+          <t>151169</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -4215,7 +4215,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,14%</t>
+          <t>91,0%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>672588</t>
+          <t>672023</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>685275</t>
+          <t>685174</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,58%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4321</t>
+          <t>4225</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18670</t>
+          <t>17561</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4435,7 +4435,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4263</t>
+          <t>5021</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4450,7 +4450,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5136</t>
+          <t>5189</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>20129</t>
+          <t>19620</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4485,7 +4485,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,99%</t>
         </is>
       </c>
     </row>
@@ -4508,12 +4508,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1130968</t>
+          <t>1132077</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1145317</t>
+          <t>1145413</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4523,12 +4523,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,63%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4543,7 +4543,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>821613</t>
+          <t>820855</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -4558,7 +4558,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,39%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -4578,12 +4578,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1955385</t>
+          <t>1955894</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1970378</t>
+          <t>1970325</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4593,7 +4593,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1235</t>
+          <t>969</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10464</t>
+          <t>9793</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2004</t>
+          <t>1997</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>12608</t>
+          <t>12561</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4793,7 +4793,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4921</t>
+          <t>4876</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>17611</t>
+          <t>18247</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4828,7 +4828,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,34%</t>
         </is>
       </c>
     </row>
@@ -4851,12 +4851,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>610242</t>
+          <t>610913</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>619471</t>
+          <t>619737</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4866,12 +4866,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,8%</t>
+          <t>99,84%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4886,12 +4886,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>725636</t>
+          <t>725683</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>736240</t>
+          <t>736247</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4901,7 +4901,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -4921,12 +4921,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1341339</t>
+          <t>1340703</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1354029</t>
+          <t>1354074</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4936,7 +4936,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -5061,7 +5061,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5121,7 +5121,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8441</t>
+          <t>7847</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5136,7 +5136,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>8319</t>
+          <t>8983</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5171,7 +5171,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,66%</t>
         </is>
       </c>
     </row>
@@ -5229,7 +5229,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1073584</t>
+          <t>1074178</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -5244,7 +5244,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,27%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1360851</t>
+          <t>1360187</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -5279,7 +5279,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -5424,12 +5424,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>15617</t>
+          <t>15253</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>36370</t>
+          <t>36061</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5439,7 +5439,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -5459,12 +5459,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>7438</t>
+          <t>7594</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>23484</t>
+          <t>24494</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5474,12 +5474,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5494,12 +5494,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>27216</t>
+          <t>27061</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>54848</t>
+          <t>54191</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5514,7 +5514,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,78%</t>
         </is>
       </c>
     </row>
@@ -5537,12 +5537,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3349352</t>
+          <t>3349661</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3370105</t>
+          <t>3370469</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5557,7 +5557,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,55%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5572,12 +5572,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3508112</t>
+          <t>3507102</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3524158</t>
+          <t>3524002</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5587,12 +5587,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,79%</t>
+          <t>99,78%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6862470</t>
+          <t>6863127</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6890102</t>
+          <t>6890257</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5622,7 +5622,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
